--- a/Planilhas/Pedidos IVA.xlsx
+++ b/Planilhas/Pedidos IVA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python_scripts\Planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python_scripts\PLANILHAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E630D239-F570-4A38-BF34-4A01FB32D3A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DCBE623-9085-4292-9A53-E8C4647C44BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{B22F4247-8A78-4CA2-917D-234C68224E18}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B22F4247-8A78-4CA2-917D-234C68224E18}"/>
   </bookViews>
   <sheets>
     <sheet name="ALTERAR PARA F5" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Item</t>
   </si>
@@ -43,7 +43,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -53,6 +53,12 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -78,13 +84,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -127,12 +148,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C4F11308-4C43-48B9-BA07-AEB362118F73}" name="Tabela1" displayName="Tabela1" ref="A1:C24" totalsRowShown="0">
-  <autoFilter ref="A1:C24" xr:uid="{C4F11308-4C43-48B9-BA07-AEB362118F73}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C4F11308-4C43-48B9-BA07-AEB362118F73}" name="Tabela1" displayName="Tabela1" ref="A1:C2" totalsRowShown="0">
+  <autoFilter ref="A1:C2" xr:uid="{C4F11308-4C43-48B9-BA07-AEB362118F73}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D0BC8C79-FDF1-4144-B598-1BCD4BB7CFD1}" name="Pedidos"/>
+    <tableColumn id="1" xr3:uid="{D0BC8C79-FDF1-4144-B598-1BCD4BB7CFD1}" name="Pedidos" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{3D9316E3-CFBE-4A9E-8B75-E0BF8E30E135}" name="Item" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{EB45FE85-7012-4F95-906A-AD0D817858AE}" name="Novo Código Imposto" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{EB45FE85-7012-4F95-906A-AD0D817858AE}" name="Novo Código Imposto" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -435,10 +456,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C176DAE8-01D4-4562-9DC5-3FF54C0846F5}">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.81640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -454,255 +475,13 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>4500033801</v>
+      <c r="A2" s="1">
+        <v>4500036663</v>
       </c>
       <c r="B2">
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>4500033822</v>
-      </c>
-      <c r="B3">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>4500033823</v>
-      </c>
-      <c r="B4">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>4500033824</v>
-      </c>
-      <c r="B5">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>4500033825</v>
-      </c>
-      <c r="B6">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>4500033826</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>4500033838</v>
-      </c>
-      <c r="B8">
-        <v>10</v>
-      </c>
-      <c r="C8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>4500033839</v>
-      </c>
-      <c r="B9">
-        <v>10</v>
-      </c>
-      <c r="C9" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>4500033840</v>
-      </c>
-      <c r="B10">
-        <v>10</v>
-      </c>
-      <c r="C10" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>4500033842</v>
-      </c>
-      <c r="B11">
-        <v>10</v>
-      </c>
-      <c r="C11" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>4500033843</v>
-      </c>
-      <c r="B12">
-        <v>10</v>
-      </c>
-      <c r="C12" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>4500033844</v>
-      </c>
-      <c r="B13">
-        <v>10</v>
-      </c>
-      <c r="C13" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>4500033846</v>
-      </c>
-      <c r="B14">
-        <v>10</v>
-      </c>
-      <c r="C14" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>4500033847</v>
-      </c>
-      <c r="B15">
-        <v>10</v>
-      </c>
-      <c r="C15" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <v>4500033848</v>
-      </c>
-      <c r="B16">
-        <v>10</v>
-      </c>
-      <c r="C16" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>4500033849</v>
-      </c>
-      <c r="B17">
-        <v>10</v>
-      </c>
-      <c r="C17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18">
-        <v>4500033850</v>
-      </c>
-      <c r="B18">
-        <v>10</v>
-      </c>
-      <c r="C18" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>4500033865</v>
-      </c>
-      <c r="B19">
-        <v>10</v>
-      </c>
-      <c r="C19" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20">
-        <v>4500033866</v>
-      </c>
-      <c r="B20">
-        <v>10</v>
-      </c>
-      <c r="C20" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21">
-        <v>4500033867</v>
-      </c>
-      <c r="B21">
-        <v>10</v>
-      </c>
-      <c r="C21" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22">
-        <v>4500033868</v>
-      </c>
-      <c r="B22">
-        <v>10</v>
-      </c>
-      <c r="C22" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23">
-        <v>4500033869</v>
-      </c>
-      <c r="B23">
-        <v>10</v>
-      </c>
-      <c r="C23" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24">
-        <v>4500033870</v>
-      </c>
-      <c r="B24">
-        <v>10</v>
-      </c>
-      <c r="C24" t="s">
         <v>3</v>
       </c>
     </row>

--- a/Planilhas/Pedidos IVA.xlsx
+++ b/Planilhas/Pedidos IVA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python_scripts\PLANILHAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DCBE623-9085-4292-9A53-E8C4647C44BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F4B11DC-BA69-4868-B3EE-4CFA39C22C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B22F4247-8A78-4CA2-917D-234C68224E18}"/>
+    <workbookView xWindow="28635" yWindow="-135" windowWidth="29130" windowHeight="15810" xr2:uid="{B22F4247-8A78-4CA2-917D-234C68224E18}"/>
   </bookViews>
   <sheets>
     <sheet name="ALTERAR PARA F5" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="4">
   <si>
     <t>Item</t>
   </si>
@@ -94,20 +94,6 @@
   <dxfs count="3">
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
@@ -134,6 +120,20 @@
         <scheme val="minor"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -148,12 +148,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C4F11308-4C43-48B9-BA07-AEB362118F73}" name="Tabela1" displayName="Tabela1" ref="A1:C2" totalsRowShown="0">
-  <autoFilter ref="A1:C2" xr:uid="{C4F11308-4C43-48B9-BA07-AEB362118F73}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C4F11308-4C43-48B9-BA07-AEB362118F73}" name="Tabela1" displayName="Tabela1" ref="A1:C13" totalsRowShown="0">
+  <autoFilter ref="A1:C13" xr:uid="{C4F11308-4C43-48B9-BA07-AEB362118F73}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D0BC8C79-FDF1-4144-B598-1BCD4BB7CFD1}" name="Pedidos" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{D0BC8C79-FDF1-4144-B598-1BCD4BB7CFD1}" name="Pedidos" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{3D9316E3-CFBE-4A9E-8B75-E0BF8E30E135}" name="Item" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{EB45FE85-7012-4F95-906A-AD0D817858AE}" name="Novo Código Imposto" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{EB45FE85-7012-4F95-906A-AD0D817858AE}" name="Novo Código Imposto" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -456,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C176DAE8-01D4-4562-9DC5-3FF54C0846F5}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.7265625" bestFit="1" customWidth="1"/>
@@ -476,12 +476,133 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
-        <v>4500036663</v>
+        <v>4500038577</v>
       </c>
       <c r="B2">
         <v>10</v>
       </c>
       <c r="C2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>4500038580</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>4500038581</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
+        <v>4500038587</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>4500038588</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
+        <v>4500038592</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
+        <v>4500038610</v>
+      </c>
+      <c r="B8">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>4500038683</v>
+      </c>
+      <c r="B9">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>4500038689</v>
+      </c>
+      <c r="B10">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
+        <v>4500038707</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
+        <v>4500038763</v>
+      </c>
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="1">
+        <v>4500038772</v>
+      </c>
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
         <v>3</v>
       </c>
     </row>
